--- a/assets/tvm/Time Value of Money Review Solutions.xlsx
+++ b/assets/tvm/Time Value of Money Review Solutions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\1 - Time Value of Money\Review\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\Financial Analytics Spring 2025\Course\1 - Time Value of Money\4 - Exercises\1 - Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69221F08-6351-41A2-94E5-518F917800A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E083EC71-F2C8-4B86-B3B9-58E4CACFD8C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" firstSheet="5" activeTab="9" xr2:uid="{6EE16BD3-821C-4EF1-8275-74C7E8006C6F}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="17472" windowHeight="10992" xr2:uid="{6EE16BD3-821C-4EF1-8275-74C7E8006C6F}"/>
   </bookViews>
   <sheets>
     <sheet name="Problem 1" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,7 @@
     <sheet name="Problem 9" sheetId="9" r:id="rId9"/>
     <sheet name="Problem 10" sheetId="10" r:id="rId10"/>
     <sheet name="Problem 11" sheetId="12" r:id="rId11"/>
-    <sheet name="Problem 12" sheetId="13" r:id="rId12"/>
-    <sheet name="Problem 13" sheetId="14" r:id="rId13"/>
+    <sheet name="Problem 12" sheetId="14" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>t</t>
   </si>
@@ -95,19 +94,16 @@
     <t>PV_30</t>
   </si>
   <si>
-    <t>Your bank loans you $10,000 for a car at 6% per year, compounded monthly. What is the effective monthly rate?</t>
-  </si>
-  <si>
-    <t>Your bank loans you $10,000 for a car at 6% per year, compounded monthly. What is the EAR?</t>
-  </si>
-  <si>
-    <t>Your bank loans you $10,000 for a car at 6% per year, compounded monthly. What is the effective semi-annual rate?</t>
-  </si>
-  <si>
     <t>You are 30 years old. You buy an asset that will begin paying your family annual payments in perpetuity when you turn 56. The first payment is $71,259 and will occur at age 56. The payments will grow 2% per year. If the annual discount rate is 7%, what is the price of the asset today?</t>
   </si>
   <si>
     <t>PV_55</t>
+  </si>
+  <si>
+    <t>Your bank loans you $10,000 for a car at 0.50% monthly. What is the effective annual rate?</t>
+  </si>
+  <si>
+    <t>Your bank loans you $10,000 for a car at 0.50% monthly. What is the effective semi-annual rate?</t>
   </si>
 </sst>
 </file>
@@ -520,17 +516,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB093BEA-A648-42CE-BD68-3F1147AAC43B}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">
         <f>PV(5%,3,,618)</f>
         <v>-533.85163589245212</v>
@@ -541,17 +537,17 @@
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="1"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="E6" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="2"/>
     </row>
   </sheetData>
@@ -562,14 +558,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21486B8E-465F-4BC7-9552-E82EA0F77970}">
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.41796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -582,7 +578,7 @@
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -595,7 +591,7 @@
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -608,7 +604,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="13"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -621,7 +617,7 @@
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="13"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -634,9 +630,9 @@
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C7" s="12">
         <f>71259/(7%-2%)</f>
@@ -647,7 +643,7 @@
         <v>=71259/(7%-2%)</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
         <v>14</v>
       </c>
@@ -671,21 +667,21 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{220B73D3-040B-427F-B983-C15ACBB61AE9}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="10">
-        <f>6%/12</f>
-        <v>5.0000000000000001E-3</v>
+        <f>(1+0.5%)^12-1</f>
+        <v>6.1677811864497611E-2</v>
       </c>
       <c r="B3" t="str">
         <f ca="1">_xlfn.FORMULATEXT(A3)</f>
-        <v>=6%/12</v>
+        <v>=(1+0.5%)^12-1</v>
       </c>
     </row>
   </sheetData>
@@ -694,33 +690,33 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AEC66D2-5FA3-474B-97B8-28F7CF8B8E6F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB1D838-7B0D-435D-A3A3-7CA5970729B8}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="11">
-        <f>6%/12</f>
-        <v>5.0000000000000001E-3</v>
+        <f>(1+0.5%)^12-1</f>
+        <v>6.1677811864497611E-2</v>
       </c>
       <c r="B3" t="str">
         <f ca="1">_xlfn.FORMULATEXT(A3)</f>
-        <v>=6%/12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+        <v>=(1+0.5%)^12-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="10">
-        <f>(1+A3)^12-1</f>
-        <v>6.1677811864497611E-2</v>
+        <f>(1+A3)^(1/2)-1</f>
+        <v>3.0377509393764601E-2</v>
       </c>
       <c r="B4" t="str">
         <f ca="1">_xlfn.FORMULATEXT(A4)</f>
-        <v>=(1+A3)^12-1</v>
+        <v>=(1+A3)^(1/2)-1</v>
       </c>
     </row>
   </sheetData>
@@ -728,44 +724,98 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB1D838-7B0D-435D-A3A3-7CA5970729B8}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2EB8F80-0B7D-4461-BE7F-137E9E4ED3D9}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="4" max="4" width="9.5234375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="11">
-        <f>6%/12</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="B3" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(A3)</f>
-        <v>=6%/12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="11">
-        <f>(1+A3)^12-1</f>
-        <v>6.1677811864497611E-2</v>
-      </c>
-      <c r="B4" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(A4)</f>
-        <v>=(1+A3)^12-1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" s="10">
-        <f>(1+A4)^(1/2)-1</f>
-        <v>3.0377509393764601E-2</v>
-      </c>
-      <c r="B5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(A5)</f>
-        <v>=(1+A4)^(1/2)-1</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="5">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <f>NPV(3%,B5:B11)</f>
+        <v>1864.8278344443806</v>
+      </c>
+      <c r="E4" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(D4)</f>
+        <v>=NPV(3%,B5:B11)</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="5">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="5">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="5">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="5">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="5">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="5">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6">
+        <v>813</v>
       </c>
     </row>
   </sheetData>
@@ -773,119 +823,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2EB8F80-0B7D-4461-BE7F-137E9E4ED3D9}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="4" max="4" width="9.53125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="5">
-        <v>0</v>
-      </c>
-      <c r="B4" s="6">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <f>NPV(3%,B5:B11)</f>
-        <v>1864.8278344443806</v>
-      </c>
-      <c r="E4" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(D4)</f>
-        <v>=NPV(3%,B5:B11)</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="5">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="5">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="5">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="5">
-        <v>4</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" s="5">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="5">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="5">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6">
-        <v>813</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33695724-D3AA-43CC-9CCC-8EB9AD62A90D}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="3" max="3" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.20703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="7" t="s">
         <v>0</v>
       </c>
@@ -893,7 +844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="5">
         <v>0</v>
       </c>
@@ -909,7 +860,7 @@
         <v>=IRR(C4:C7)</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -917,7 +868,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="5">
         <v>2</v>
       </c>
@@ -925,7 +876,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -942,14 +893,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DC9DC4-A504-4433-AB41-5547E50D133E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">
         <f>PV(6%,5,167)</f>
         <v>-703.46475218947501</v>
@@ -967,14 +918,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B79301F-0124-4FD4-8394-666EC2CB97E8}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">
         <f>PMT(3%,7,-100)</f>
         <v>16.050635375427195</v>
@@ -992,17 +943,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2434C9F6-12CB-4DAB-AADE-CE878FA43E0F}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1015625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">
         <f>FV(9%,10,107)</f>
         <v>-1625.6434797928523</v>
@@ -1021,14 +972,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF9BF29-76CD-4F36-BEC0-FCB7782774B4}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="8">
         <f>RATE(7,35,-120)</f>
         <v>0.2185595967244193</v>
@@ -1046,14 +997,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB0EF04-E3E6-4BA7-81EF-A23D3F0755F2}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1015625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.20703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.68359375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="13" t="s">
         <v>9</v>
       </c>
@@ -1070,7 +1021,7 @@
       <c r="L1" s="13"/>
       <c r="M1" s="13"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -1085,7 +1036,7 @@
       <c r="L2" s="13"/>
       <c r="M2" s="13"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -1100,7 +1051,7 @@
       <c r="L3" s="13"/>
       <c r="M3" s="13"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1115,7 +1066,7 @@
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="13"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -1130,7 +1081,7 @@
       <c r="L5" s="13"/>
       <c r="M5" s="13"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="13"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1145,7 +1096,7 @@
       <c r="L6" s="13"/>
       <c r="M6" s="13"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
         <v>11</v>
       </c>
@@ -1158,7 +1109,7 @@
         <v>=PV(6%,12,76159)</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" t="s">
         <v>13</v>
       </c>
@@ -1171,7 +1122,7 @@
         <v>=60-25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" t="s">
         <v>12</v>
       </c>
@@ -1195,17 +1146,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AB5D978-97BB-4E54-92AA-33D39B805EE9}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1015625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9">
         <f>181/8%</f>
         <v>2262.5</v>
